--- a/mappings/DPP-DPPO/DPP-DPPO.xlsx
+++ b/mappings/DPP-DPPO/DPP-DPPO.xlsx
@@ -85,7 +85,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -104,6 +104,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -503,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -923,7 +926,7 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>dpp-comp</t>
+          <t>dpp-info</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
@@ -1016,6 +1019,150 @@
       <c r="N7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> For product-level roles, keep DPP’s AgentRole on dpp:Product; additionally mint DPPO responsibleActor on each DPPInformation item to meet DPPO’s auditability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DPP_DPPO_0006</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>DPP</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>ObjectProperty</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>http://w3id.org/dpp#hasComponent</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>dpp</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>hasComponent</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>DPPO</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>ObjectProperty</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>http://w3id.org/dppo/ontology/dpp-odp/hasPart</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>dpp-odp</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>hasPart</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>subproperty_of</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>source_to_target</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>DPP asserts partonomy directly at the product level through dpp:hasComponent (domain dpp:Product, range dpp:Component), whereas DPPO uses the generic dpp-odp:hasPart. The DPP property is therefore a specialisation of the DPPO one. Stated in the Product Component and Partonomy Alignment section of the accompanying paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>DPP_DPPO_0007</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>DPP</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>http://w3id.org/dpp#Manufacturer</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>dpp</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>DPPO</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>http://w3id.org/dppo/ontology/dpp-prov/ValueChainActor</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>dpp-prov</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>ValueChainActor</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>subclass_of</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t>source_to_target</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>DPPO defines ValueChainActor as an actor that is an active participant of the value chain of a product, explicitly exemplified by a manufacturer. dpp:Manufacturer, an entity responsible for producing products, components or materials, is therefore a specialisation. Additional mapping, not discussed in the paper.</t>
         </is>
       </c>
     </row>

--- a/mappings/DPP-DPPO/DPP-DPPO.xlsx
+++ b/mappings/DPP-DPPO/DPP-DPPO.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
     <row r="3" ht="57.6" customFormat="1" customHeight="1" s="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DPP_DPPO_0001</t>
+          <t>DPP_DPPO_0002</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>http://w3id.org/dpp#Product</t>
+          <t>http://w3id.org/dpp#Component</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
@@ -705,17 +705,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>http://w3id.org/dppo/ontology/dpp-odp/Product</t>
+          <t>http://w3id.org/dppo/ontology/dpp-core/Component</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>dpp-odp</t>
+          <t>dpp-core</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
@@ -730,14 +730,14 @@
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>DPP is stricter: product≠material; DPPO keeps them possibly overlapping. Subclass mapping preserves DPPO’s sector-agnostic stance without breaking DPP's disjointness.</t>
+          <t>DPPO defines a component as a product that is itself a component of another product, and places material and substance under product as well, so a DPPO component may at the same time be a DPPO material or substance. The DPP ontology places its component class under dpp:Product and keeps dpp:Material in a branch coordinate with it under dpp:PhysicalEntity, so a DPP component is not a material. The DPP class is therefore the narrower of the two and is aligned as a subclass rather than equated. Stated in the section on the semantic alignment of core classes in the accompanying paper.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="86.40000000000001" customFormat="1" customHeight="1" s="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DPP_DPPO_0002</t>
+          <t>DPP_DPPO_0005</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>http://w3id.org/dpp#Component</t>
+          <t>http://w3id.org/dpp#Agent</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
@@ -777,17 +777,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>http://w3id.org/dppo/ontology/dpp-core/Component</t>
+          <t>http://w3id.org/dppo/ontology/dpp-prov/Actor</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>dpp-core</t>
+          <t>dpp-prov</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
@@ -802,14 +802,14 @@
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>Both represent part-whole relationships. Structural correspondence: both as subclasses of Product with part-of links. Modular alignment allows complex product breakdowns in DPP (e.g., building elements into sub-components) to map into DPPO’s composition pattern.</t>
+          <t xml:space="preserve"> For product-level roles, keep DPP’s AgentRole on dpp:Product; additionally mint DPPO responsibleActor on each DPPInformation item to meet DPPO’s auditability.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="86.40000000000001" customFormat="1" customHeight="1" s="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DPP_DPPO_0003</t>
+          <t>DPP_DPPO_0006</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>http://w3id.org/dpp#Material</t>
+          <t>ObjectProperty</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>http://w3id.org/dpp#hasComponent</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>hasComponent</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
@@ -844,27 +844,27 @@
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>http://w3id.org/dppo/ontology/dpp-core/Material</t>
+          <t>ObjectProperty</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>http://w3id.org/dppo/ontology/dpp-odp/hasPart</t>
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>dpp-core</t>
+          <t>dpp-odp</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>hasPart</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>subclass_of</t>
+          <t>subproperty_of</t>
         </is>
       </c>
       <c r="M5" s="1" t="inlineStr">
@@ -874,14 +874,14 @@
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>Semantically equivalent: both capture the matter constituting products/parts. Subclass mapping (dppo:Material ⊑ dppo:Product) reflects DPPO’s flexibility; DPP’s modular placement preserves structure. Alignment preserves CE relevance (resource loops, recyclability).</t>
+          <t>DPP asserts partonomy directly at the product level through dpp:hasComponent (domain dpp:Product, range dpp:Component), whereas DPPO uses the generic dpp-odp:hasPart. The DPP property is therefore a specialisation of the DPPO one. Stated in the Product Component and Partonomy Alignment section of the accompanying paper.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28.8" customFormat="1" customHeight="1" s="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DPP_DPPO_0004</t>
+          <t>DPP_DPPO_0007</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
@@ -894,9 +894,9 @@
           <t>Class</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>http://w3id.org/dpp#MaterialComposition</t>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>http://w3id.org/dpp#Manufacturer</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>MaterialComposition</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
@@ -919,19 +919,19 @@
           <t>Class</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>http://w3id.org/dppo/ontology/dpp-info/CompositionInformation</t>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>http://w3id.org/dppo/ontology/dpp-prov/ValueChainActor</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>dpp-info</t>
+          <t>dpp-prov</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>CompositionInformation</t>
+          <t>ValueChainActor</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
@@ -946,226 +946,11 @@
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>Both model partonomy as first-class nodes; quantitative details remain attached to the reified link.</t>
+          <t>DPPO defines ValueChainActor as an actor that is an active participant of the value chain of a product, explicitly exemplified by a manufacturer. dpp:Manufacturer, an entity responsible for producing products, components or materials, is therefore a specialisation. Additional mapping, not discussed in the paper.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="57.6" customFormat="1" customHeight="1" s="1">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>DPP_DPPO_0005</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>DPP</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>http://w3id.org/dpp#Agent</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>dpp</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Agent</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>DPPO</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>http://w3id.org/dppo/ontology/dpp-prov/Actor</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>dpp-prov</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>Actor</t>
-        </is>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>equivalent_class</t>
-        </is>
-      </c>
-      <c r="M7" s="1" t="inlineStr">
-        <is>
-          <t>bidirectional</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> For product-level roles, keep DPP’s AgentRole on dpp:Product; additionally mint DPPO responsibleActor on each DPPInformation item to meet DPPO’s auditability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>DPP_DPPO_0006</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>DPP</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>ObjectProperty</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>http://w3id.org/dpp#hasComponent</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>dpp</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>hasComponent</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>DPPO</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>ObjectProperty</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>http://w3id.org/dppo/ontology/dpp-odp/hasPart</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>dpp-odp</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>hasPart</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>subproperty_of</t>
-        </is>
-      </c>
-      <c r="M8" s="1" t="inlineStr">
-        <is>
-          <t>source_to_target</t>
-        </is>
-      </c>
-      <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>DPP asserts partonomy directly at the product level through dpp:hasComponent (domain dpp:Product, range dpp:Component), whereas DPPO uses the generic dpp-odp:hasPart. The DPP property is therefore a specialisation of the DPPO one. Stated in the Product Component and Partonomy Alignment section of the accompanying paper.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>DPP_DPPO_0007</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>DPP</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>http://w3id.org/dpp#Manufacturer</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>dpp</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Manufacturer</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>DPPO</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>http://w3id.org/dppo/ontology/dpp-prov/ValueChainActor</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>dpp-prov</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>ValueChainActor</t>
-        </is>
-      </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>subclass_of</t>
-        </is>
-      </c>
-      <c r="M9" s="1" t="inlineStr">
-        <is>
-          <t>source_to_target</t>
-        </is>
-      </c>
-      <c r="N9" s="1" t="inlineStr">
-        <is>
-          <t>DPPO defines ValueChainActor as an actor that is an active participant of the value chain of a product, explicitly exemplified by a manufacturer. dpp:Manufacturer, an entity responsible for producing products, components or materials, is therefore a specialisation. Additional mapping, not discussed in the paper.</t>
-        </is>
-      </c>
-    </row>
+    <row r="7" ht="57.6" customFormat="1" customHeight="1" s="1"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="M3:M5001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1182,16 +967,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" location="Product" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" location="Component" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" location="Material" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" location="MaterialComposition" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" location="Agent" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" location="Component" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
